--- a/topics/Exam/dsda/List_of_Points.xlsx
+++ b/topics/Exam/dsda/List_of_Points.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10208"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10215"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ben/Documents/Studies/Business Administration (M. A.)/Analytical Skills for Business/Projects/Analytical-Skills-for-Business/topics/Exam/dsda/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9E1B0C8D-5200-C241-A81D-5EB505705FEB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2E160A01-4619-9641-946C-55741AF04E1E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="17180" xr2:uid="{1DCBEC8E-A8BB-E948-AC40-85FEABBAF676}"/>
+    <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="17100" xr2:uid="{1DCBEC8E-A8BB-E948-AC40-85FEABBAF676}"/>
   </bookViews>
   <sheets>
     <sheet name="Points" sheetId="1" r:id="rId1"/>
@@ -267,6 +267,26 @@
   <dxfs count="7">
     <dxf>
       <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right/>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
         <left/>
         <right/>
         <top style="thin">
@@ -296,43 +316,6 @@
     <dxf>
       <border diagonalUp="0" diagonalDown="0">
         <left/>
-        <right/>
-        <top/>
-        <bottom/>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <bottom style="medium">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right/>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical style="thin">
-          <color indexed="64"/>
-        </vertical>
-        <horizontal style="thin">
-          <color indexed="64"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <border diagonalUp="0" diagonalDown="0">
-        <left/>
         <right style="thin">
           <color indexed="64"/>
         </right>
@@ -364,6 +347,23 @@
         <bottom style="medium">
           <color indexed="64"/>
         </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <bottom style="medium">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right/>
+        <top/>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
       </border>
     </dxf>
   </dxfs>
@@ -380,13 +380,13 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{3B097F9C-BABC-2740-A815-F856C8014392}" name="Table1" displayName="Table1" ref="A1:D16" totalsRowShown="0" headerRowDxfId="2" headerRowBorderDxfId="3" tableBorderDxfId="6">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{3B097F9C-BABC-2740-A815-F856C8014392}" name="Table1" displayName="Table1" ref="A1:D16" totalsRowShown="0" headerRowDxfId="6" headerRowBorderDxfId="5" tableBorderDxfId="4">
   <autoFilter ref="A1:D16" xr:uid="{3B097F9C-BABC-2740-A815-F856C8014392}"/>
   <tableColumns count="4">
-    <tableColumn id="1" xr3:uid="{5FE26FD7-53DF-5C4C-99E5-96E40C6BFA9E}" name="Name" dataDxfId="5"/>
-    <tableColumn id="4" xr3:uid="{C7FFF10F-15D3-C545-8615-DA4766737C8A}" name="Document No." dataDxfId="0"/>
+    <tableColumn id="1" xr3:uid="{5FE26FD7-53DF-5C4C-99E5-96E40C6BFA9E}" name="Name" dataDxfId="3"/>
+    <tableColumn id="4" xr3:uid="{C7FFF10F-15D3-C545-8615-DA4766737C8A}" name="Document No." dataDxfId="2"/>
     <tableColumn id="3" xr3:uid="{69E4E74B-C695-C947-A8BC-2BA0A9DBEFEC}" name="Matriculation number" dataDxfId="1"/>
-    <tableColumn id="2" xr3:uid="{DAAF135C-485B-AB4D-9CC6-F63E52BD802F}" name="Points (max. 90)" dataDxfId="4"/>
+    <tableColumn id="2" xr3:uid="{DAAF135C-485B-AB4D-9CC6-F63E52BD802F}" name="Points (max. 90)" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -771,7 +771,7 @@
         <v>400878749</v>
       </c>
       <c r="D4" s="3">
-        <v>43</v>
+        <v>45</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.2">
